--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LIEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B7D15D-B2F0-49D2-B4C5-0A20BDECBB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15330" windowHeight="1560" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Raw_run1" sheetId="1" r:id="rId1"/>
+    <sheet name="Raw_run2" sheetId="2" r:id="rId2"/>
+    <sheet name="COMBINE" sheetId="3" r:id="rId3"/>
+    <sheet name="loadout" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="120">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -307,13 +310,103 @@
   </si>
   <si>
     <t>Unit.Value</t>
+  </si>
+  <si>
+    <t>pH 7.8</t>
+  </si>
+  <si>
+    <t>pH 7.6</t>
+  </si>
+  <si>
+    <t>pH 8.2</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>L7</t>
+  </si>
+  <si>
+    <t>L8</t>
+  </si>
+  <si>
+    <t>L9</t>
+  </si>
+  <si>
+    <t>L10</t>
+  </si>
+  <si>
+    <t>L12</t>
+  </si>
+  <si>
+    <t>L14</t>
+  </si>
+  <si>
+    <t>L16</t>
+  </si>
+  <si>
+    <t>L18</t>
+  </si>
+  <si>
+    <t>L11</t>
+  </si>
+  <si>
+    <t>L13</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>L17</t>
+  </si>
+  <si>
+    <t>BATCH #161</t>
+  </si>
+  <si>
+    <t>Salinity</t>
+  </si>
+  <si>
+    <r>
+      <t>Total CO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Source Sans Pro"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>micromol/kg</t>
+  </si>
+  <si>
+    <t>Total Alkalinity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,16 +415,48 @@
       <charset val="177"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9.35"/>
+      <color rgb="FF000000"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.35"/>
+      <color rgb="FF000000"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7.5"/>
+      <color rgb="FF000000"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFD8E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -339,14 +464,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCFD8E7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCFD8E7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCFD8E7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCFD8E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCFD8E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,7 +789,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1363,7 +1525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2779,4 +2941,2176 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615746BB-BF41-4DE8-A482-95D690C6CCEC}">
+  <dimension ref="A1:J65"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3031.21</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I2" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3463.0140000000001</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="1">
+        <v>9.94</v>
+      </c>
+      <c r="I3" s="1">
+        <v>50.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3430.63</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1">
+        <v>9.85</v>
+      </c>
+      <c r="I4" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3441.5259999999998</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I5" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3436.183</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>9.86</v>
+      </c>
+      <c r="I6" s="1">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3156.7539999999999</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>9.06</v>
+      </c>
+      <c r="I7" s="1">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3151.0970000000002</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="I8" s="1">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3448.4090000000001</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="I9" s="1">
+        <v>50.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3416.462</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="I10" s="1">
+        <v>50.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3352.33</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="I11" s="1">
+        <v>50.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3356.8710000000001</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="I12" s="1">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3075.3119999999999</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8.83</v>
+      </c>
+      <c r="I13" s="1">
+        <v>50.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3090.05</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="I14" s="1">
+        <v>50.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3434.1860000000001</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>9.86</v>
+      </c>
+      <c r="I15" s="1">
+        <v>50.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3443.9250000000002</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I16" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3355.585</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="I17" s="1">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3357.7559999999999</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>9.64</v>
+      </c>
+      <c r="I18" s="1">
+        <v>50.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3091.328</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="I19" s="1">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3262.8110000000001</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9.36</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50.03</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3381.1930000000002</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I21" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="1">
+        <v>50.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="1">
+        <v>50.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3117.4360000000001</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="I24" s="1">
+        <v>50</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3417.7339999999999</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="I25" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3362.4870000000001</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
+        <v>9.65</v>
+      </c>
+      <c r="I26" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3397.3980000000001</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="1">
+        <v>9.75</v>
+      </c>
+      <c r="I27" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3379.7310000000002</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I28" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2968.4670000000001</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>8.52</v>
+      </c>
+      <c r="I29" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2960.7370000000001</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="I30" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3345.201</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="I31" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3332.422</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
+        <v>9.56</v>
+      </c>
+      <c r="I32" s="1">
+        <v>50.08</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3453.683</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>9.91</v>
+      </c>
+      <c r="I33" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3468.0880000000002</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="I34" s="1">
+        <v>50.08</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2920.239</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="I35" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2979.9259999999999</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="I36" s="1">
+        <v>50</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3357.9430000000002</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1">
+        <v>9.64</v>
+      </c>
+      <c r="I37" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3336.895</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1">
+        <v>9.58</v>
+      </c>
+      <c r="I38" s="1">
+        <v>50</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3369.5859999999998</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
+        <v>9.67</v>
+      </c>
+      <c r="I39" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3380.6729999999998</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I40" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3079.2919999999999</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>8.84</v>
+      </c>
+      <c r="I41" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3175.1210000000001</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>9.11</v>
+      </c>
+      <c r="I42" s="1">
+        <v>50</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3051.8710000000001</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="I43" s="1">
+        <v>50.04</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3031.21</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I44" s="1">
+        <v>50</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3463.0140000000001</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="1">
+        <v>9.94</v>
+      </c>
+      <c r="I45" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3430.63</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="1">
+        <v>9.85</v>
+      </c>
+      <c r="I46" s="1">
+        <v>50</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3441.5259999999998</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I47" s="1">
+        <v>50</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3436.183</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="1">
+        <v>9.86</v>
+      </c>
+      <c r="I48" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3156.7539999999999</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1">
+        <v>9.06</v>
+      </c>
+      <c r="I49" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3151.0970000000002</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H50" s="1">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="I50" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3448.4090000000001</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="I51" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>3416.462</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="I52" s="1">
+        <v>50.04</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>3352.33</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="I53" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>3356.8710000000001</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="1">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="I54" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>3075.3119999999999</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H55" s="1">
+        <v>8.83</v>
+      </c>
+      <c r="I55" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3090.05</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H56" s="1">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="I56" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>3434.1860000000001</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="1">
+        <v>9.86</v>
+      </c>
+      <c r="I57" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3443.9250000000002</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="1">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I58" s="1">
+        <v>50</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>3355.585</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="1">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="I59" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>3357.7559999999999</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="1">
+        <v>9.64</v>
+      </c>
+      <c r="I60" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>3091.328</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="1">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="I61" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3262.8110000000001</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="1">
+        <v>9.36</v>
+      </c>
+      <c r="I62" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>3381.1930000000002</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H63" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I63" s="1">
+        <v>50</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B583D8D2-8418-4236-9FC5-B879D10DDF52}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45778</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45781</v>
+      </c>
+      <c r="B3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45783</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45788</v>
+      </c>
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45791</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="27.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="6"/>
+      <c r="C11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="3">
+        <v>33.356000000000002</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2037.38</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2207.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B7D15D-B2F0-49D2-B4C5-0A20BDECBB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0387625C-8AB6-4BAB-B0C9-8E17AB4C7EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="121">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>Total Alkalinity</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -2945,2023 +2948,1833 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615746BB-BF41-4DE8-A482-95D690C6CCEC}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1">
         <v>3031.21</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8.6999999999999993</v>
       </c>
       <c r="H2" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I2" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
         <v>3463.0140000000001</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>9.94</v>
       </c>
       <c r="H3" s="1">
-        <v>9.94</v>
-      </c>
-      <c r="I3" s="1">
         <v>50.02</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
         <v>3430.63</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G4" s="1">
+        <v>9.85</v>
       </c>
       <c r="H4" s="1">
-        <v>9.85</v>
-      </c>
-      <c r="I4" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
         <v>3441.5259999999998</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
+        <v>9.8800000000000008</v>
       </c>
       <c r="H5" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I5" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
         <v>3436.183</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>9.86</v>
       </c>
       <c r="H6" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="I6" s="1">
         <v>50.01</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
         <v>3156.7539999999999</v>
       </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>9.06</v>
       </c>
       <c r="H7" s="1">
-        <v>9.06</v>
-      </c>
-      <c r="I7" s="1">
         <v>50.01</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
         <v>3151.0970000000002</v>
       </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>9.0399999999999991</v>
       </c>
       <c r="H8" s="1">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="I8" s="1">
         <v>50.01</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
         <v>3448.4090000000001</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9.9</v>
       </c>
       <c r="H9" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="I9" s="1">
         <v>50.03</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
         <v>3416.462</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9.81</v>
       </c>
       <c r="H10" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="I10" s="1">
         <v>50.04</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
         <v>3352.33</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>9.6199999999999992</v>
       </c>
       <c r="H11" s="1">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="I11" s="1">
         <v>50.03</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
         <v>3356.8710000000001</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>9.6300000000000008</v>
       </c>
       <c r="H12" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I12" s="1">
         <v>50.01</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
         <v>3075.3119999999999</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>8.83</v>
       </c>
       <c r="H13" s="1">
-        <v>8.83</v>
-      </c>
-      <c r="I13" s="1">
         <v>50.02</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
         <v>3090.05</v>
       </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G14" s="1">
+        <v>8.8699999999999992</v>
       </c>
       <c r="H14" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="I14" s="1">
         <v>50.02</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
         <v>3434.1860000000001</v>
       </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>9.86</v>
       </c>
       <c r="H15" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="I15" s="1">
         <v>50.03</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
         <v>3443.9250000000002</v>
       </c>
+      <c r="E16" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>9.8800000000000008</v>
       </c>
       <c r="H16" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I16" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1">
         <v>3355.585</v>
       </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G17" s="1">
+        <v>9.6300000000000008</v>
       </c>
       <c r="H17" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I17" s="1">
         <v>50.01</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1">
         <v>3357.7559999999999</v>
       </c>
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G18" s="1">
+        <v>9.64</v>
       </c>
       <c r="H18" s="1">
-        <v>9.64</v>
-      </c>
-      <c r="I18" s="1">
         <v>50.05</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1">
         <v>3091.328</v>
       </c>
+      <c r="E19" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>8.8699999999999992</v>
       </c>
       <c r="H19" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="I19" s="1">
         <v>50.01</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1">
         <v>3262.8110000000001</v>
       </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>9.36</v>
       </c>
       <c r="H20" s="1">
-        <v>9.36</v>
-      </c>
-      <c r="I20" s="1">
         <v>50.03</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1">
         <v>3381.1930000000002</v>
       </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>9.6999999999999993</v>
       </c>
       <c r="H21" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I21" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="1">
+      <c r="H22" s="1">
         <v>50.05</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="1">
+      <c r="H23" s="1">
         <v>50.05</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1">
         <v>3117.4360000000001</v>
       </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G24" s="1">
+        <v>8.9499999999999993</v>
       </c>
       <c r="H24" s="1">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="I24" s="1">
         <v>50</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1">
         <v>3417.7339999999999</v>
       </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G25" s="1">
+        <v>9.81</v>
       </c>
       <c r="H25" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="I25" s="1">
         <v>50.02</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1">
         <v>3362.4870000000001</v>
       </c>
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9.65</v>
       </c>
       <c r="H26" s="1">
-        <v>9.65</v>
-      </c>
-      <c r="I26" s="1">
         <v>50.05</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="1">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1">
         <v>3397.3980000000001</v>
       </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G27" s="1">
+        <v>9.75</v>
       </c>
       <c r="H27" s="1">
-        <v>9.75</v>
-      </c>
-      <c r="I27" s="1">
         <v>50.01</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1">
         <v>3379.7310000000002</v>
       </c>
+      <c r="E28" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9.6999999999999993</v>
       </c>
       <c r="H28" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I28" s="1">
         <v>50.05</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1">
         <v>2968.4670000000001</v>
       </c>
+      <c r="E29" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8.52</v>
       </c>
       <c r="H29" s="1">
-        <v>8.52</v>
-      </c>
-      <c r="I29" s="1">
         <v>50.05</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1">
         <v>2960.7370000000001</v>
       </c>
+      <c r="E30" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G30" s="1">
+        <v>8.5</v>
       </c>
       <c r="H30" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="I30" s="1">
         <v>50.01</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1">
         <v>3345.201</v>
       </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G31" s="1">
+        <v>9.6</v>
       </c>
       <c r="H31" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="I31" s="1">
         <v>50.02</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1">
         <v>3332.422</v>
       </c>
+      <c r="E32" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G32" s="1">
+        <v>9.56</v>
       </c>
       <c r="H32" s="1">
-        <v>9.56</v>
-      </c>
-      <c r="I32" s="1">
         <v>50.08</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1">
         <v>3453.683</v>
       </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G33" s="1">
+        <v>9.91</v>
       </c>
       <c r="H33" s="1">
-        <v>9.91</v>
-      </c>
-      <c r="I33" s="1">
         <v>50.02</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1">
         <v>3468.0880000000002</v>
       </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G34" s="1">
+        <v>9.9499999999999993</v>
       </c>
       <c r="H34" s="1">
-        <v>9.9499999999999993</v>
-      </c>
-      <c r="I34" s="1">
         <v>50.08</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1">
         <v>2920.239</v>
       </c>
+      <c r="E35" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G35" s="1">
+        <v>8.3800000000000008</v>
       </c>
       <c r="H35" s="1">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="I35" s="1">
         <v>50.02</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1">
         <v>2979.9259999999999</v>
       </c>
+      <c r="E36" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>8.5500000000000007</v>
       </c>
       <c r="H36" s="1">
-        <v>8.5500000000000007</v>
-      </c>
-      <c r="I36" s="1">
         <v>50</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1">
         <v>3357.9430000000002</v>
       </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G37" s="1">
+        <v>9.64</v>
       </c>
       <c r="H37" s="1">
-        <v>9.64</v>
-      </c>
-      <c r="I37" s="1">
         <v>50.02</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1">
         <v>3336.895</v>
       </c>
+      <c r="E38" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>9.58</v>
       </c>
       <c r="H38" s="1">
-        <v>9.58</v>
-      </c>
-      <c r="I38" s="1">
         <v>50</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" s="1">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1">
         <v>3369.5859999999998</v>
       </c>
+      <c r="E39" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>9.67</v>
       </c>
       <c r="H39" s="1">
-        <v>9.67</v>
-      </c>
-      <c r="I39" s="1">
         <v>50.05</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1">
         <v>3380.6729999999998</v>
       </c>
+      <c r="E40" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>9.6999999999999993</v>
       </c>
       <c r="H40" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I40" s="1">
         <v>50.03</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="1">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1">
         <v>3079.2919999999999</v>
       </c>
+      <c r="E41" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>8.84</v>
       </c>
       <c r="H41" s="1">
-        <v>8.84</v>
-      </c>
-      <c r="I41" s="1">
         <v>50.01</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1">
         <v>3175.1210000000001</v>
       </c>
+      <c r="E42" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G42" s="1">
+        <v>9.11</v>
       </c>
       <c r="H42" s="1">
-        <v>9.11</v>
-      </c>
-      <c r="I42" s="1">
         <v>50</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1">
         <v>3051.8710000000001</v>
       </c>
+      <c r="E43" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G43" s="1">
+        <v>8.76</v>
       </c>
       <c r="H43" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="I43" s="1">
         <v>50.04</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1">
         <v>3031.21</v>
       </c>
+      <c r="E44" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G44" s="1">
+        <v>8.6999999999999993</v>
       </c>
       <c r="H44" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I44" s="1">
         <v>50</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="1">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1">
         <v>3463.0140000000001</v>
       </c>
+      <c r="E45" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G45" s="1">
+        <v>9.94</v>
       </c>
       <c r="H45" s="1">
-        <v>9.94</v>
-      </c>
-      <c r="I45" s="1">
         <v>50.02</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1">
         <v>3430.63</v>
       </c>
+      <c r="E46" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G46" s="1">
+        <v>9.85</v>
       </c>
       <c r="H46" s="1">
-        <v>9.85</v>
-      </c>
-      <c r="I46" s="1">
         <v>50</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1">
         <v>3441.5259999999998</v>
       </c>
+      <c r="E47" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G47" s="1">
+        <v>9.8800000000000008</v>
       </c>
       <c r="H47" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I47" s="1">
         <v>50</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1">
         <v>3436.183</v>
       </c>
+      <c r="E48" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G48" s="1">
+        <v>9.86</v>
       </c>
       <c r="H48" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="I48" s="1">
         <v>50.01</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="1">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1">
         <v>3156.7539999999999</v>
       </c>
+      <c r="E49" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G49" s="1">
+        <v>9.06</v>
       </c>
       <c r="H49" s="1">
-        <v>9.06</v>
-      </c>
-      <c r="I49" s="1">
         <v>50.01</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E50" s="1">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1">
         <v>3151.0970000000002</v>
       </c>
+      <c r="E50" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G50" s="1">
+        <v>9.0399999999999991</v>
       </c>
       <c r="H50" s="1">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="I50" s="1">
         <v>50.01</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1">
         <v>3448.4090000000001</v>
       </c>
+      <c r="E51" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G51" s="1">
+        <v>9.9</v>
       </c>
       <c r="H51" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="I51" s="1">
         <v>50.03</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="1">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1">
         <v>3416.462</v>
       </c>
+      <c r="E52" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G52" s="1">
+        <v>9.81</v>
       </c>
       <c r="H52" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="I52" s="1">
         <v>50.04</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E53" s="1">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1">
         <v>3352.33</v>
       </c>
+      <c r="E53" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>9.6199999999999992</v>
       </c>
       <c r="H53" s="1">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="I53" s="1">
         <v>50.03</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E54" s="1">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1">
         <v>3356.8710000000001</v>
       </c>
+      <c r="E54" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G54" s="1">
+        <v>9.6300000000000008</v>
       </c>
       <c r="H54" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I54" s="1">
         <v>50.01</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1">
         <v>3075.3119999999999</v>
       </c>
+      <c r="E55" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G55" s="1">
+        <v>8.83</v>
       </c>
       <c r="H55" s="1">
-        <v>8.83</v>
-      </c>
-      <c r="I55" s="1">
         <v>50.02</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1">
         <v>3090.05</v>
       </c>
+      <c r="E56" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G56" s="1">
+        <v>8.8699999999999992</v>
       </c>
       <c r="H56" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="I56" s="1">
         <v>50.02</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1">
         <v>3434.1860000000001</v>
       </c>
+      <c r="E57" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F57" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G57" s="1">
+        <v>9.86</v>
       </c>
       <c r="H57" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="I57" s="1">
         <v>50.03</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1">
         <v>3443.9250000000002</v>
       </c>
+      <c r="E58" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>9.8800000000000008</v>
       </c>
       <c r="H58" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I58" s="1">
         <v>50</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="1">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1">
         <v>3355.585</v>
       </c>
+      <c r="E59" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G59" s="1">
+        <v>9.6300000000000008</v>
       </c>
       <c r="H59" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I59" s="1">
         <v>50.01</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="1">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1">
         <v>3357.7559999999999</v>
       </c>
+      <c r="E60" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F60" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G60" s="1">
+        <v>9.64</v>
       </c>
       <c r="H60" s="1">
-        <v>9.64</v>
-      </c>
-      <c r="I60" s="1">
         <v>50.05</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E61" s="1">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1">
         <v>3091.328</v>
       </c>
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G61" s="1">
+        <v>8.8699999999999992</v>
       </c>
       <c r="H61" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="I61" s="1">
         <v>50.01</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="1">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1">
         <v>3262.8110000000001</v>
       </c>
+      <c r="E62" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G62" s="1">
+        <v>9.36</v>
       </c>
       <c r="H62" s="1">
-        <v>9.36</v>
-      </c>
-      <c r="I62" s="1">
         <v>50.03</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I62" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" s="1">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1">
         <v>3381.1930000000002</v>
       </c>
+      <c r="E63" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G63" s="1">
+        <v>9.6999999999999993</v>
       </c>
       <c r="H63" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I63" s="1">
         <v>50</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I64" s="1">
+      <c r="H64" s="1">
         <v>50.05</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I64" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I65" s="1">
+      <c r="H65" s="1">
         <v>50.05</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="I65" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0387625C-8AB6-4BAB-B0C9-8E17AB4C7EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C8B356-73A6-4E10-8341-F234FA4CACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_run1" sheetId="1" r:id="rId1"/>
@@ -4796,10 +4796,10 @@
         <v>96</v>
       </c>
       <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
         <v>94</v>
-      </c>
-      <c r="D1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C8B356-73A6-4E10-8341-F234FA4CACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9FAEE1-829A-475F-B476-BB053F25E7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_run1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="122">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>L15_2</t>
   </si>
 </sst>
 </file>
@@ -3768,7 +3771,7 @@
         <v>62</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9FAEE1-829A-475F-B476-BB053F25E7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F42D5B0-F111-4C41-9595-80E5FEBF955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="121">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -403,9 +403,6 @@
   </si>
   <si>
     <t>Time</t>
-  </si>
-  <si>
-    <t>L15_2</t>
   </si>
 </sst>
 </file>
@@ -2951,7 +2948,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615746BB-BF41-4DE8-A482-95D690C6CCEC}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -2965,7 +2962,7 @@
     <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -2991,1795 +2988,1591 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3117.4360000000001</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="I2" s="1">
+        <v>50</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3417.7339999999999</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="I3" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3362.4870000000001</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1">
+        <v>9.65</v>
+      </c>
+      <c r="I4" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3397.3980000000001</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9.75</v>
+      </c>
+      <c r="I5" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3379.7310000000002</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I6" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2968.4670000000001</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>8.52</v>
+      </c>
+      <c r="I7" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2960.7370000000001</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="I8" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3345.201</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="I9" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3332.422</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>9.56</v>
+      </c>
+      <c r="I10" s="1">
+        <v>50.08</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3453.683</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>9.91</v>
+      </c>
+      <c r="I11" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3468.0880000000002</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="I12" s="1">
+        <v>50.08</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2920.239</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="I13" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2979.9259999999999</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="I14" s="1">
+        <v>50</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3357.9430000000002</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>9.64</v>
+      </c>
+      <c r="I15" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3336.895</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>9.58</v>
+      </c>
+      <c r="I16" s="1">
+        <v>50</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3369.5859999999998</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>9.67</v>
+      </c>
+      <c r="I17" s="1">
+        <v>50.05</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3380.6729999999998</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I18" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3079.2919999999999</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1">
+        <v>8.84</v>
+      </c>
+      <c r="I19" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3175.1210000000001</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9.11</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3051.8710000000001</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="I21" s="1">
+        <v>50.04</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
         <v>3031.21</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="F22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="1">
         <v>8.6999999999999993</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I22" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="J22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
         <v>3463.0140000000001</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1">
         <v>9.94</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I23" s="1">
         <v>50.02</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="J23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
         <v>3430.63</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="F24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
         <v>9.85</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I24" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="J24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
         <v>3441.5259999999998</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1">
         <v>9.8800000000000008</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I25" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="J25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="D26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
         <v>3436.183</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="F26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
         <v>9.86</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I26" s="1">
         <v>50.01</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="J26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="D27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
         <v>3156.7539999999999</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="1">
         <v>9.06</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I27" s="1">
         <v>50.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="J27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
         <v>3151.0970000000002</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="F28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1">
         <v>9.0399999999999991</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I28" s="1">
         <v>50.01</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="J28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="D29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
         <v>3448.4090000000001</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="1">
         <v>9.9</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I29" s="1">
         <v>50.03</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="J29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="D30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
         <v>3416.462</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="F30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="1">
         <v>9.81</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I30" s="1">
         <v>50.04</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="J30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="D31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
         <v>3352.33</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="F31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
         <v>9.6199999999999992</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I31" s="1">
         <v>50.03</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="J31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="D32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
         <v>3356.8710000000001</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="F32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
         <v>9.6300000000000008</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I32" s="1">
         <v>50.01</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="J32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="D33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
         <v>3075.3119999999999</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="F33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
         <v>8.83</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I33" s="1">
         <v>50.02</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="J33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="D34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
         <v>3090.05</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="F34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I34" s="1">
         <v>50.02</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="J34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="D35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
         <v>3434.1860000000001</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="F35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
         <v>9.86</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I35" s="1">
         <v>50.03</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="J35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="D36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
         <v>3443.9250000000002</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="F36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1">
         <v>9.8800000000000008</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I36" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="J36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
         <v>3355.585</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="F37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1">
         <v>9.6300000000000008</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I37" s="1">
         <v>50.01</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="J37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="D38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1">
         <v>3357.7559999999999</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="F38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1">
         <v>9.64</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I38" s="1">
         <v>50.05</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="J38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="D39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
         <v>3091.328</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="F39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I39" s="1">
         <v>50.01</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="J39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="D40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
         <v>3262.8110000000001</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="F40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
         <v>9.36</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I40" s="1">
         <v>50.03</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="J40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="D41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
         <v>3381.1930000000002</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="F41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
         <v>9.6999999999999993</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I41" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="J41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="F42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I42" s="1">
         <v>50.05</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="J42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="F43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I43" s="1">
         <v>50.05</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3117.4360000000001</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="1">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="H24" s="1">
-        <v>50</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1">
-        <v>3417.7339999999999</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="H25" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1">
-        <v>3362.4870000000001</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="1">
-        <v>9.65</v>
-      </c>
-      <c r="H26" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3397.3980000000001</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="1">
-        <v>9.75</v>
-      </c>
-      <c r="H27" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3379.7310000000002</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="H28" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2968.4670000000001</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="1">
-        <v>8.52</v>
-      </c>
-      <c r="H29" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2960.7370000000001</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="H30" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3345.201</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G31" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="H31" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3332.422</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="1">
-        <v>9.56</v>
-      </c>
-      <c r="H32" s="1">
-        <v>50.08</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1">
-        <v>3453.683</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="1">
-        <v>9.91</v>
-      </c>
-      <c r="H33" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3468.0880000000002</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G34" s="1">
-        <v>9.9499999999999993</v>
-      </c>
-      <c r="H34" s="1">
-        <v>50.08</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2920.239</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="1">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="H35" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1">
-        <v>2979.9259999999999</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G36" s="1">
-        <v>8.5500000000000007</v>
-      </c>
-      <c r="H36" s="1">
-        <v>50</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1">
-        <v>3357.9430000000002</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="1">
-        <v>9.64</v>
-      </c>
-      <c r="H37" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1">
-        <v>3336.895</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" s="1">
-        <v>9.58</v>
-      </c>
-      <c r="H38" s="1">
-        <v>50</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1">
-        <v>3369.5859999999998</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="1">
-        <v>9.67</v>
-      </c>
-      <c r="H39" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1">
-        <v>3380.6729999999998</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="H40" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1">
-        <v>3079.2919999999999</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="1">
-        <v>8.84</v>
-      </c>
-      <c r="H41" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1">
-        <v>3175.1210000000001</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="1">
-        <v>9.11</v>
-      </c>
-      <c r="H42" s="1">
-        <v>50</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1">
-        <v>3051.8710000000001</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="H43" s="1">
-        <v>50.04</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1">
-        <v>3031.21</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G44" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H44" s="1">
-        <v>50</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1">
-        <v>3463.0140000000001</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="1">
-        <v>9.94</v>
-      </c>
-      <c r="H45" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1">
-        <v>3430.63</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G46" s="1">
-        <v>9.85</v>
-      </c>
-      <c r="H46" s="1">
-        <v>50</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1">
-        <v>3441.5259999999998</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="H47" s="1">
-        <v>50</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1">
-        <v>3436.183</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="H48" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="J43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1">
-        <v>3156.7539999999999</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="1">
-        <v>9.06</v>
-      </c>
-      <c r="H49" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1">
-        <v>3151.0970000000002</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G50" s="1">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="H50" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1">
-        <v>3448.4090000000001</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="H51" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1">
-        <v>3416.462</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="H52" s="1">
-        <v>50.04</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1">
-        <v>3352.33</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G53" s="1">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="H53" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1">
-        <v>3356.8710000000001</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G54" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="H54" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1">
-        <v>3075.3119999999999</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="1">
-        <v>8.83</v>
-      </c>
-      <c r="H55" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1">
-        <v>3090.05</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G56" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="H56" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1">
-        <v>3434.1860000000001</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="H57" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1">
-        <v>3443.9250000000002</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="H58" s="1">
-        <v>50</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1">
-        <v>3355.585</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="H59" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1">
-        <v>3357.7559999999999</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="1">
-        <v>9.64</v>
-      </c>
-      <c r="H60" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1">
-        <v>3091.328</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="H61" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1">
-        <v>3262.8110000000001</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="1">
-        <v>9.36</v>
-      </c>
-      <c r="H62" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1">
-        <v>3381.1930000000002</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G63" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="H63" s="1">
-        <v>50</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H64" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H65" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F42D5B0-F111-4C41-9595-80E5FEBF955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF755104-DC3B-4C84-9D11-8B0571C83D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="121">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -2948,7 +2948,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615746BB-BF41-4DE8-A482-95D690C6CCEC}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -4269,68 +4269,26 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I43" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
@@ -4551,28 +4509,6 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF755104-DC3B-4C84-9D11-8B0571C83D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF26F253-03ED-4E56-B549-E1EF7B383B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_run1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="122">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>L15_2</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>3</v>
@@ -3220,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>3</v>

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF26F253-03ED-4E56-B549-E1EF7B383B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6637125-302D-4651-9348-9A61AB81D195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_run1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="124">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -406,6 +406,12 @@
   </si>
   <si>
     <t>L15_2</t>
+  </si>
+  <si>
+    <t>control_3_#161</t>
+  </si>
+  <si>
+    <t>control_1_#161</t>
   </si>
 </sst>
 </file>
@@ -2956,7 +2962,7 @@
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
@@ -3607,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>3</v>
@@ -4247,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>3</v>

--- a/supplementary/Alkalinity_test.xlsx
+++ b/supplementary/Alkalinity_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6637125-302D-4651-9348-9A61AB81D195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3106DB77-332E-42D6-BA91-F0B2CFF8381A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="121">
   <si>
     <t>2026-07-14 15:50:49 UTC+3</t>
   </si>
@@ -163,15 +163,6 @@
   </si>
   <si>
     <t>control _1_ #161</t>
-  </si>
-  <si>
-    <t>2026-07-14 11:57:18 UTC+3</t>
-  </si>
-  <si>
-    <t>invalid</t>
-  </si>
-  <si>
-    <t>2026-07-14 11:54:48 UTC+3</t>
   </si>
   <si>
     <t>2026-07-14 20:14:06 UTC+3</t>
@@ -802,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K23"/>
+  <dimension ref="A2:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1464,72 +1455,6 @@
         <v>6</v>
       </c>
       <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1538,41 +1463,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>89</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>90</v>
-      </c>
-      <c r="G1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
@@ -1599,13 +1524,13 @@
     </row>
     <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -1632,13 +1557,13 @@
     </row>
     <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -1665,13 +1590,13 @@
     </row>
     <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -1698,13 +1623,13 @@
     </row>
     <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -1731,13 +1656,13 @@
     </row>
     <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>3</v>
@@ -1764,13 +1689,13 @@
     </row>
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
@@ -1797,13 +1722,13 @@
     </row>
     <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>3</v>
@@ -1830,13 +1755,13 @@
     </row>
     <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>3</v>
@@ -1863,13 +1788,13 @@
     </row>
     <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -1896,13 +1821,13 @@
     </row>
     <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>3</v>
@@ -1929,13 +1854,13 @@
     </row>
     <row r="13" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>3</v>
@@ -1962,13 +1887,13 @@
     </row>
     <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
@@ -1995,13 +1920,13 @@
     </row>
     <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>3</v>
@@ -2028,13 +1953,13 @@
     </row>
     <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -2061,13 +1986,13 @@
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
@@ -2094,13 +2019,13 @@
     </row>
     <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>3</v>
@@ -2127,13 +2052,13 @@
     </row>
     <row r="19" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -2160,13 +2085,13 @@
     </row>
     <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>3</v>
@@ -2193,13 +2118,13 @@
     </row>
     <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>3</v>
@@ -2223,732 +2148,6 @@
         <v>6</v>
       </c>
       <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>3031.21</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I22" s="1">
-        <v>50</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1">
-        <v>3463.0140000000001</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="1">
-        <v>9.94</v>
-      </c>
-      <c r="I23" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>3430.63</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="1">
-        <v>9.85</v>
-      </c>
-      <c r="I24" s="1">
-        <v>50</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="1">
-        <v>3441.5259999999998</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H25" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I25" s="1">
-        <v>50</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3436.183</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="I26" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="1">
-        <v>3156.7539999999999</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="1">
-        <v>9.06</v>
-      </c>
-      <c r="I27" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3151.0970000000002</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H28" s="1">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="I28" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3448.4090000000001</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="I29" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
-        <v>3416.462</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H30" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="I30" s="1">
-        <v>50.04</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3352.33</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H31" s="1">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="I31" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>3356.8710000000001</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I32" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3075.3119999999999</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="1">
-        <v>8.83</v>
-      </c>
-      <c r="I33" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
-        <v>3090.05</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H34" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="I34" s="1">
-        <v>50.02</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1">
-        <v>3434.1860000000001</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="1">
-        <v>9.86</v>
-      </c>
-      <c r="I35" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1">
-        <v>3443.9250000000002</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H36" s="1">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="I36" s="1">
-        <v>50</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="1">
-        <v>3355.585</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H37" s="1">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I37" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="1">
-        <v>3357.7559999999999</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H38" s="1">
-        <v>9.64</v>
-      </c>
-      <c r="I38" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" s="1">
-        <v>3091.328</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H39" s="1">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="I39" s="1">
-        <v>50.01</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="1">
-        <v>3262.8110000000001</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H40" s="1">
-        <v>9.36</v>
-      </c>
-      <c r="I40" s="1">
-        <v>50.03</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="1">
-        <v>3381.1930000000002</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I41" s="1">
-        <v>50</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I43" s="1">
-        <v>50.05</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K43" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2968,44 +2167,44 @@
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>90</v>
-      </c>
-      <c r="F1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
@@ -3031,13 +2230,13 @@
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -3063,13 +2262,13 @@
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -3095,13 +2294,13 @@
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -3127,13 +2326,13 @@
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -3159,13 +2358,13 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>3</v>
@@ -3191,13 +2390,13 @@
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
@@ -3223,13 +2422,13 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>3</v>
@@ -3255,13 +2454,13 @@
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>3</v>
@@ -3287,13 +2486,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -3319,13 +2518,13 @@
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>3</v>
@@ -3351,13 +2550,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>3</v>
@@ -3383,13 +2582,13 @@
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
@@ -3415,13 +2614,13 @@
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>3</v>
@@ -3447,13 +2646,13 @@
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -3479,13 +2678,13 @@
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
@@ -3511,13 +2710,13 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>3</v>
@@ -3543,13 +2742,13 @@
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
@@ -3575,13 +2774,13 @@
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>3</v>
@@ -3607,13 +2806,13 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>3</v>
@@ -4253,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>3</v>
@@ -4534,13 +3733,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -4548,13 +3747,13 @@
         <v>45778</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4562,13 +3761,13 @@
         <v>45781</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4576,13 +3775,13 @@
         <v>45783</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4590,13 +3789,13 @@
         <v>45786</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4604,13 +3803,13 @@
         <v>45788</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4618,41 +3817,41 @@
         <v>45791</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" ht="27.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="6"/>
       <c r="C11" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B12" s="3">
         <v>33.356000000000002</v>
